--- a/physics/first_term/labs/lab1/calculations.xlsx
+++ b/physics/first_term/labs/lab1/calculations.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miwm64/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miwm64/itmo/practice/itmo_cse/physics/first_term/labs/lab1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62059417-3FDA-6C4E-A02C-35CB086BEF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8CD9D5-E23E-6547-B9B4-AE95C0DD8662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="16380" xr2:uid="{5C85809A-1FFE-D64B-9DD2-0FF3932A7C0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -402,10 +402,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02AA4E43-2E75-1B44-B789-DD2E4921BA47}">
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:L233"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="30.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>1</v>
       </c>
@@ -414,14 +417,15 @@
       </c>
       <c r="C1">
         <f>B1-$E$1</f>
-        <v>16</v>
+        <v>16.454545454545453</v>
       </c>
       <c r="D1">
         <f>C1^2</f>
-        <v>256</v>
+        <v>270.75206611570246</v>
       </c>
       <c r="E1">
-        <v>24</v>
+        <f>G1</f>
+        <v>23.545454545454547</v>
       </c>
       <c r="G1">
         <f>SUM(B1:B55)/55</f>
@@ -429,14 +433,22 @@
       </c>
       <c r="H1">
         <f>SUM(C1:C55)/55</f>
-        <v>-0.45454545454545453</v>
+        <v>-1.2918958832001822E-15</v>
       </c>
       <c r="I1">
         <f>SQRT(SUM(D1:D55)/55)</f>
-        <v>12.308902912489435</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>12.300507279736189</v>
+      </c>
+      <c r="K1">
+        <f>ROUND(C1,0)</f>
+        <v>16</v>
+      </c>
+      <c r="L1">
+        <f>ROUND(D1,0)</f>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -444,15 +456,23 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C65" si="0">B2-$E$1</f>
+        <f t="shared" ref="C2:C55" si="0">B2-$E$1</f>
+        <v>-3.5454545454545467</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:D55" si="1">C2^2</f>
+        <v>12.570247933884307</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:K55" si="2">ROUND(C2,0)</f>
         <v>-4</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D65" si="1">C2^2</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L2">
+        <f t="shared" ref="L2:L55" si="3">ROUND(D2,0)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -461,14 +481,22 @@
       </c>
       <c r="C3">
         <f t="shared" si="0"/>
+        <v>-9.5454545454545467</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>91.115702479338864</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
-      <c r="D3">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L3">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -477,14 +505,26 @@
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
+        <v>1.4545454545454533</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>2.115702479338839</v>
+      </c>
+      <c r="G4">
+        <f>1/(I1*(SQRT(2*PI())))</f>
+        <v>3.243299413014037E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -493,14 +533,22 @@
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
+        <v>37.454545454545453</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>1402.8429752066115</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L5">
+        <f t="shared" si="3"/>
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>6</v>
       </c>
@@ -509,14 +557,22 @@
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
+        <v>39.454545454545453</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>1556.6611570247933</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -525,14 +581,22 @@
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
+        <v>-14.545454545454547</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>211.57024793388433</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
         <v>-15</v>
       </c>
-      <c r="D7">
-        <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8</v>
       </c>
@@ -541,14 +605,22 @@
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
+        <v>7.4545454545454533</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>55.570247933884275</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9</v>
       </c>
@@ -557,14 +629,22 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
+        <v>-0.54545454545454675</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0.29752066115702619</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="D9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10</v>
       </c>
@@ -573,14 +653,22 @@
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
+        <v>13.454545454545453</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>181.02479338842971</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="D10">
-        <f t="shared" si="1"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11</v>
       </c>
@@ -589,14 +677,22 @@
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
+        <v>-5.5454545454545467</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>30.752066115702494</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>12</v>
       </c>
@@ -605,14 +701,22 @@
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
+        <v>3.4545454545454533</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>11.933884297520652</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>13</v>
       </c>
@@ -621,14 +725,22 @@
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
+        <v>-11.545454545454547</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>133.29752066115705</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
         <v>-12</v>
       </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>14</v>
       </c>
@@ -637,14 +749,22 @@
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
+        <v>-0.54545454545454675</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>0.29752066115702619</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="D14">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>15</v>
       </c>
@@ -653,14 +773,22 @@
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
+        <v>4.4545454545454533</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>19.842975206611559</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D15">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>16</v>
       </c>
@@ -669,14 +797,22 @@
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
+        <v>-1.5454545454545467</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>2.3884297520661195</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
-      <c r="D16">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>17</v>
       </c>
@@ -685,14 +821,22 @@
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
+        <v>-13.545454545454547</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>183.47933884297524</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
         <v>-14</v>
       </c>
-      <c r="D17">
-        <f t="shared" si="1"/>
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>18</v>
       </c>
@@ -701,14 +845,22 @@
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
+        <v>8.4545454545454533</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>71.479338842975181</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="D18">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L18">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>19</v>
       </c>
@@ -717,14 +869,22 @@
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
+        <v>-15.545454545454547</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>241.66115702479343</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
         <v>-16</v>
       </c>
-      <c r="D19">
-        <f t="shared" si="1"/>
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>20</v>
       </c>
@@ -733,14 +893,22 @@
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
+        <v>-6.5454545454545467</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>42.842975206611584</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
         <v>-7</v>
       </c>
-      <c r="D20">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>21</v>
       </c>
@@ -749,14 +917,22 @@
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
+        <v>-5.5454545454545467</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>30.752066115702494</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="D21">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>22</v>
       </c>
@@ -765,14 +941,22 @@
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
+        <v>12.454545454545453</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>155.11570247933881</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D22">
-        <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>23</v>
       </c>
@@ -781,14 +965,22 @@
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
+        <v>-7.5454545454545467</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>56.933884297520677</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
         <v>-8</v>
       </c>
-      <c r="D23">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L23">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>24</v>
       </c>
@@ -797,14 +989,22 @@
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
+        <v>-0.54545454545454675</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>0.29752066115702619</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="D24">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>25</v>
       </c>
@@ -813,14 +1013,22 @@
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
+        <v>-16.545454545454547</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>273.75206611570252</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="2"/>
         <v>-17</v>
       </c>
-      <c r="D25">
-        <f t="shared" si="1"/>
-        <v>289</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>26</v>
       </c>
@@ -829,14 +1037,22 @@
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
+        <v>-17.545454545454547</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="1"/>
+        <v>307.84297520661164</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
         <v>-18</v>
       </c>
-      <c r="D26">
-        <f t="shared" si="1"/>
-        <v>324</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L26">
+        <f t="shared" si="3"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>27</v>
       </c>
@@ -845,14 +1061,22 @@
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
+        <v>8.4545454545454533</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>71.479338842975181</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="D27">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>28</v>
       </c>
@@ -861,14 +1085,22 @@
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
+        <v>6.4545454545454533</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>41.661157024793368</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D28">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L28">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>29</v>
       </c>
@@ -877,14 +1109,22 @@
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
+        <v>3.4545454545454533</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="1"/>
+        <v>11.933884297520652</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D29">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L29">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>30</v>
       </c>
@@ -893,14 +1133,22 @@
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
+        <v>27.454545454545453</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>753.75206611570241</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="D30">
-        <f t="shared" si="1"/>
-        <v>729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L30">
+        <f t="shared" si="3"/>
+        <v>754</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>31</v>
       </c>
@@ -909,14 +1157,22 @@
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
+        <v>2.4545454545454533</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>6.024793388429746</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D31">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L31">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32</v>
       </c>
@@ -925,14 +1181,22 @@
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
+        <v>5.4545454545454533</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="1"/>
+        <v>29.752066115702466</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D32">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L32">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>33</v>
       </c>
@@ -941,14 +1205,22 @@
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
+        <v>3.4545454545454533</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="1"/>
+        <v>11.933884297520652</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D33">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L33">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34</v>
       </c>
@@ -957,14 +1229,22 @@
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
+        <v>-3.5454545454545467</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="1"/>
+        <v>12.570247933884307</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="D34">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L34">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>35</v>
       </c>
@@ -973,14 +1253,22 @@
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
+        <v>6.4545454545454533</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>41.661157024793368</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D35">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L35">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>36</v>
       </c>
@@ -989,14 +1277,22 @@
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
+        <v>-9.5454545454545467</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>91.115702479338864</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
-      <c r="D36">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L36">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>37</v>
       </c>
@@ -1005,14 +1301,22 @@
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
+        <v>-7.5454545454545467</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="1"/>
+        <v>56.933884297520677</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="2"/>
         <v>-8</v>
       </c>
-      <c r="D37">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L37">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>38</v>
       </c>
@@ -1021,14 +1325,22 @@
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
+        <v>-3.5454545454545467</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>12.570247933884307</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="D38">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L38">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>39</v>
       </c>
@@ -1037,14 +1349,22 @@
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
+        <v>-14.545454545454547</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="1"/>
+        <v>211.57024793388433</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="2"/>
         <v>-15</v>
       </c>
-      <c r="D39">
-        <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L39">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>40</v>
       </c>
@@ -1053,14 +1373,22 @@
       </c>
       <c r="C40">
         <f t="shared" si="0"/>
+        <v>-20.545454545454547</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="1"/>
+        <v>422.11570247933889</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="2"/>
         <v>-21</v>
       </c>
-      <c r="D40">
-        <f t="shared" si="1"/>
-        <v>441</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L40">
+        <f t="shared" si="3"/>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>41</v>
       </c>
@@ -1069,14 +1397,22 @@
       </c>
       <c r="C41">
         <f t="shared" si="0"/>
+        <v>-7.5454545454545467</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="1"/>
+        <v>56.933884297520677</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="2"/>
         <v>-8</v>
       </c>
-      <c r="D41">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L41">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>42</v>
       </c>
@@ -1085,14 +1421,22 @@
       </c>
       <c r="C42">
         <f t="shared" si="0"/>
+        <v>-7.5454545454545467</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="1"/>
+        <v>56.933884297520677</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="2"/>
         <v>-8</v>
       </c>
-      <c r="D42">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L42">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>43</v>
       </c>
@@ -1101,14 +1445,22 @@
       </c>
       <c r="C43">
         <f t="shared" si="0"/>
+        <v>-8.5454545454545467</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="1"/>
+        <v>73.024793388429771</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="2"/>
         <v>-9</v>
       </c>
-      <c r="D43">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L43">
+        <f t="shared" si="3"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>44</v>
       </c>
@@ -1117,14 +1469,22 @@
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
+        <v>-1.5454545454545467</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="1"/>
+        <v>2.3884297520661195</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
-      <c r="D44">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L44">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>45</v>
       </c>
@@ -1133,14 +1493,22 @@
       </c>
       <c r="C45">
         <f t="shared" si="0"/>
+        <v>-7.5454545454545467</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="1"/>
+        <v>56.933884297520677</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="2"/>
         <v>-8</v>
       </c>
-      <c r="D45">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L45">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>46</v>
       </c>
@@ -1149,14 +1517,22 @@
       </c>
       <c r="C46">
         <f t="shared" si="0"/>
+        <v>-9.5454545454545467</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="1"/>
+        <v>91.115702479338864</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
-      <c r="D46">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L46">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>47</v>
       </c>
@@ -1165,14 +1541,22 @@
       </c>
       <c r="C47">
         <f t="shared" si="0"/>
+        <v>23.454545454545453</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="1"/>
+        <v>550.11570247933878</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="D47">
-        <f t="shared" si="1"/>
-        <v>529</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L47">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>48</v>
       </c>
@@ -1181,14 +1565,22 @@
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
+        <v>-9.5454545454545467</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="1"/>
+        <v>91.115702479338864</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
-      <c r="D48">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L48">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>49</v>
       </c>
@@ -1197,14 +1589,22 @@
       </c>
       <c r="C49">
         <f t="shared" si="0"/>
+        <v>7.4545454545454533</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="1"/>
+        <v>55.570247933884275</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D49">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L49">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>50</v>
       </c>
@@ -1213,14 +1613,22 @@
       </c>
       <c r="C50">
         <f t="shared" si="0"/>
+        <v>5.4545454545454533</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="1"/>
+        <v>29.752066115702466</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D50">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L50">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>51</v>
       </c>
@@ -1229,14 +1637,22 @@
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
+        <v>-2.5454545454545467</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="1"/>
+        <v>6.4793388429752135</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="2"/>
         <v>-3</v>
       </c>
-      <c r="D51">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L51">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>52</v>
       </c>
@@ -1245,14 +1661,22 @@
       </c>
       <c r="C52">
         <f t="shared" si="0"/>
+        <v>2.4545454545454533</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="1"/>
+        <v>6.024793388429746</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D52">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L52">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>53</v>
       </c>
@@ -1261,14 +1685,22 @@
       </c>
       <c r="C53">
         <f t="shared" si="0"/>
+        <v>5.4545454545454533</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="1"/>
+        <v>29.752066115702466</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D53">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L53">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>54</v>
       </c>
@@ -1277,14 +1709,22 @@
       </c>
       <c r="C54">
         <f t="shared" si="0"/>
+        <v>1.4545454545454533</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="1"/>
+        <v>2.115702479338839</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D54">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L54">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>55</v>
       </c>
@@ -1293,25 +1733,39 @@
       </c>
       <c r="C55">
         <f t="shared" si="0"/>
+        <v>-9.5454545454545467</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="1"/>
+        <v>91.115702479338864</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
-      <c r="D55">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L55">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B56">
         <f>24</f>
         <v>24</v>
       </c>
       <c r="C56">
         <f>SUM(C1:C55)</f>
-        <v>-25</v>
+        <v>-7.1054273576010019E-14</v>
       </c>
       <c r="D56">
-        <f>ROUND(SQRT(SUM(D1:D55)/54), 0)</f>
-        <v>12</v>
+        <f>SQRT(SUM(D1:D55)/54)</f>
+        <v>12.413878407024015</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D57">
+        <f>SUM(D1:D55)</f>
+        <v>8321.636363636364</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
@@ -1319,12 +1773,12 @@
         <v>230</v>
       </c>
       <c r="C230">
-        <f t="shared" ref="C194:C233" si="2">B230-$E$1</f>
-        <v>-24</v>
+        <f t="shared" ref="C230:C233" si="4">B230-$E$1</f>
+        <v>-23.545454545454547</v>
       </c>
       <c r="D230">
-        <f t="shared" ref="D194:D233" si="3">C230^2</f>
-        <v>576</v>
+        <f t="shared" ref="D230:D233" si="5">C230^2</f>
+        <v>554.38842975206614</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
@@ -1332,12 +1786,12 @@
         <v>231</v>
       </c>
       <c r="C231">
-        <f t="shared" si="2"/>
-        <v>-24</v>
+        <f t="shared" si="4"/>
+        <v>-23.545454545454547</v>
       </c>
       <c r="D231">
-        <f t="shared" si="3"/>
-        <v>576</v>
+        <f t="shared" si="5"/>
+        <v>554.38842975206614</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
@@ -1345,12 +1799,12 @@
         <v>232</v>
       </c>
       <c r="C232">
-        <f t="shared" si="2"/>
-        <v>-24</v>
+        <f t="shared" si="4"/>
+        <v>-23.545454545454547</v>
       </c>
       <c r="D232">
-        <f t="shared" si="3"/>
-        <v>576</v>
+        <f t="shared" si="5"/>
+        <v>554.38842975206614</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
@@ -1358,12 +1812,12 @@
         <v>233</v>
       </c>
       <c r="C233">
-        <f t="shared" si="2"/>
-        <v>-24</v>
+        <f t="shared" si="4"/>
+        <v>-23.545454545454547</v>
       </c>
       <c r="D233">
-        <f t="shared" si="3"/>
-        <v>576</v>
+        <f t="shared" si="5"/>
+        <v>554.38842975206614</v>
       </c>
     </row>
   </sheetData>

--- a/physics/first_term/labs/lab1/calculations.xlsx
+++ b/physics/first_term/labs/lab1/calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miwm64/itmo/practice/itmo_cse/physics/first_term/labs/lab1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8CD9D5-E23E-6547-B9B4-AE95C0DD8662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4101439-1809-F244-9864-BADB93CA5F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="16380" xr2:uid="{5C85809A-1FFE-D64B-9DD2-0FF3932A7C0D}"/>
+    <workbookView xWindow="4680" yWindow="760" windowWidth="24960" windowHeight="16380" xr2:uid="{5C85809A-1FFE-D64B-9DD2-0FF3932A7C0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -406,6 +406,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="30.5" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -427,6 +428,10 @@
         <f>G1</f>
         <v>23.545454545454547</v>
       </c>
+      <c r="F1">
+        <f>SUM(B1:B55)</f>
+        <v>1295</v>
+      </c>
       <c r="G1">
         <f>SUM(B1:B55)/55</f>
         <v>23.545454545454547</v>
@@ -462,6 +467,14 @@
       <c r="D2">
         <f t="shared" ref="D2:D55" si="1">C2^2</f>
         <v>12.570247933884307</v>
+      </c>
+      <c r="G2">
+        <f>40-E1</f>
+        <v>16.454545454545453</v>
+      </c>
+      <c r="H2">
+        <f>G2*G2</f>
+        <v>270.75206611570246</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K55" si="2">ROUND(C2,0)</f>
